--- a/Result/profitability/2462.xlsx
+++ b/Result/profitability/2462.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07500000000000002</v>
+        <v>0.03750000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>12.2025</v>
+        <v>12.20125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09625000000000003</v>
+        <v>0.02625000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>13.1375</v>
+        <v>12.83</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0.22625</v>
+        <v>0.17625</v>
       </c>
       <c r="N4" t="n">
-        <v>13.09375</v>
+        <v>12.73625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2775</v>
+        <v>0.345</v>
       </c>
       <c r="N5" t="n">
-        <v>13.415</v>
+        <v>12.795</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.515</v>
+        <v>0.42375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.98</v>
+        <v>13.67875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6537500000000001</v>
+        <v>0.5974999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>15.695</v>
+        <v>15.645</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8087500000000001</v>
+        <v>0.7837499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>16.1475</v>
+        <v>16.35875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2462</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D75" t="n">
+        <v>947</v>
+      </c>
+      <c r="E75" t="n">
+        <v>110</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07250000000000004</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.81625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.690000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1942528735632185</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7397260273972603</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.959999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3231270358306189</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
